--- a/results/cross_platform/glass_crossplatform_recurrence_score_check.xlsx
+++ b/results/cross_platform/glass_crossplatform_recurrence_score_check.xlsx
@@ -9152,12 +9152,12 @@
       <c r="A1" t="inlineStr"/>
       <c r="B1" t="inlineStr">
         <is>
+          <t>RECURRENCE_SCORE_NEW</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>RECURRENCE_SCORE_OLD</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>RECURRENCE_SCORE_NEW</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -9214,16 +9214,16 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0.2389333756092782</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.1582037276469229</v>
+      </c>
+      <c r="D4" t="n">
         <v>0.240397942741943</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>-0.1500761234768787</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.2389333756092782</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-0.1582037276469229</v>
       </c>
       <c r="F4" t="n">
         <v>0.3904740662188217</v>
@@ -9239,16 +9239,16 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>0.4186236303465016</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.2803409295250794</v>
+      </c>
+      <c r="D5" t="n">
         <v>0.4213211981181357</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>-0.2764734625958086</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.4186236303465016</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.2803409295250794</v>
       </c>
       <c r="F5" t="n">
         <v>0.6977946607139442</v>
@@ -9264,16 +9264,16 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>0.1031628800766884</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.2410013876109127</v>
+      </c>
+      <c r="D6" t="n">
         <v>0.1041018816463419</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>-0.2389124700544563</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.1031628800766884</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-0.2410013876109127</v>
       </c>
       <c r="F6" t="n">
         <v>0.3430143517007981</v>
@@ -9289,16 +9289,16 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>0.1104106568912585</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.1546104531382986</v>
+      </c>
+      <c r="D7" t="n">
         <v>0.1142460350346406</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>-0.149983326062978</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.1104106568912585</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.1546104531382986</v>
       </c>
       <c r="F7" t="n">
         <v>0.2642293610976186</v>
@@ -9314,16 +9314,16 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>0.2846935889811661</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.284606768786414</v>
+      </c>
+      <c r="D8" t="n">
         <v>0.2841583568809227</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>-0.2845214296518401</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.2846935889811661</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-0.284606768786414</v>
       </c>
       <c r="F8" t="n">
         <v>0.5686797865327629</v>
@@ -9339,16 +9339,16 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>-0.1622287444208738</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.2129853227518551</v>
+      </c>
+      <c r="D9" t="n">
         <v>-0.1693598200285555</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>-0.2119463198024142</v>
-      </c>
-      <c r="D9" t="n">
-        <v>-0.1622287444208738</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-0.2129853227518551</v>
       </c>
       <c r="F9" t="n">
         <v>0.0425864997738587</v>
@@ -9364,16 +9364,16 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>0.1912893637207302</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.07801463484070409</v>
+      </c>
+      <c r="D10" t="n">
         <v>0.1924642580416767</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>-0.06779512544267557</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.1912893637207302</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.07801463484070409</v>
       </c>
       <c r="F10" t="n">
         <v>0.2602593834843522</v>
@@ -9389,16 +9389,16 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>-0.1201316340112936</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.1139290280247435</v>
+      </c>
+      <c r="D11" t="n">
         <v>-0.1116642827241812</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>-0.1078520893461407</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-0.1201316340112936</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-0.1139290280247435</v>
       </c>
       <c r="F11" t="n">
         <v>-0.003812193378040563</v>
@@ -9414,16 +9414,16 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>-0.02612520254484102</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.3564512319361562</v>
+      </c>
+      <c r="D12" t="n">
         <v>-0.02236279691412402</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>-0.3487543690089078</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-0.02612520254484102</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-0.3564512319361562</v>
       </c>
       <c r="F12" t="n">
         <v>0.3263915720947838</v>
@@ -9439,16 +9439,16 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>-0.0148334077929097</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.2622758733878187</v>
+      </c>
+      <c r="D13" t="n">
         <v>0.001947079540060903</v>
       </c>
-      <c r="C13" t="n">
+      <c r="E13" t="n">
         <v>-0.2530797989043716</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0148334077929097</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.2622758733878187</v>
       </c>
       <c r="F13" t="n">
         <v>0.2550268784444325</v>
@@ -9464,16 +9464,16 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>0.362260812993377</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.1440724958488375</v>
+      </c>
+      <c r="D14" t="n">
         <v>0.364308717530012</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>-0.132736588112333</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.362260812993377</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.1440724958488375</v>
       </c>
       <c r="F14" t="n">
         <v>0.497045305642345</v>
@@ -9489,16 +9489,16 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>-0.05447064829799875</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.2669192621499784</v>
+      </c>
+      <c r="D15" t="n">
         <v>-0.03801902216935421</v>
       </c>
-      <c r="C15" t="n">
+      <c r="E15" t="n">
         <v>-0.2554941064035065</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-0.05447064829799875</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-0.2669192621499784</v>
       </c>
       <c r="F15" t="n">
         <v>0.2174750842341523</v>
@@ -9514,16 +9514,16 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>0.1672733642809029</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.257452499557023</v>
+      </c>
+      <c r="D16" t="n">
         <v>0.1754240228823155</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
         <v>-0.2563375017761938</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.1672733642809029</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-0.257452499557023</v>
       </c>
       <c r="F16" t="n">
         <v>0.4317615246585093</v>
@@ -9539,16 +9539,16 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>0.3029046549234217</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.05339875913855685</v>
+      </c>
+      <c r="D17" t="n">
         <v>0.3041333494939715</v>
       </c>
-      <c r="C17" t="n">
+      <c r="E17" t="n">
         <v>0.05606249116732531</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.3029046549234217</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.05339875913855685</v>
       </c>
       <c r="F17" t="n">
         <v>0.2480708583266462</v>
@@ -9564,16 +9564,16 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>0.2247257816529631</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.2431719911016697</v>
+      </c>
+      <c r="D18" t="n">
         <v>0.2357144312869733</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
         <v>-0.2324350132476665</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.2247257816529631</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-0.2431719911016697</v>
       </c>
       <c r="F18" t="n">
         <v>0.4681494445346397</v>
@@ -9589,16 +9589,16 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>0.1601192618869867</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.3230081488034363</v>
+      </c>
+      <c r="D19" t="n">
         <v>0.1745181502648471</v>
       </c>
-      <c r="C19" t="n">
+      <c r="E19" t="n">
         <v>-0.313748353062365</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.1601192618869867</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-0.3230081488034363</v>
       </c>
       <c r="F19" t="n">
         <v>0.4882665033272121</v>
@@ -9614,16 +9614,16 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>0.43794511786803</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.2647378225718699</v>
+      </c>
+      <c r="D20" t="n">
         <v>0.4431521062380919</v>
       </c>
-      <c r="C20" t="n">
+      <c r="E20" t="n">
         <v>-0.2535692991396751</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.43794511786803</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-0.2647378225718699</v>
       </c>
       <c r="F20" t="n">
         <v>0.6967214053777669</v>
@@ -9639,16 +9639,16 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>-0.130187309392525</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.1510484500080377</v>
+      </c>
+      <c r="D21" t="n">
         <v>-0.1199295756593415</v>
       </c>
-      <c r="C21" t="n">
+      <c r="E21" t="n">
         <v>-0.1459773140351692</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-0.130187309392525</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-0.1510484500080377</v>
       </c>
       <c r="F21" t="n">
         <v>0.02604773837582769</v>
@@ -9664,16 +9664,16 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>-0.3568226956404821</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.2495757160200518</v>
+      </c>
+      <c r="D22" t="n">
         <v>-0.3491258501548439</v>
       </c>
-      <c r="C22" t="n">
+      <c r="E22" t="n">
         <v>-0.243424511026862</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-0.3568226956404821</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-0.2495757160200518</v>
       </c>
       <c r="F22" t="n">
         <v>-0.1057013391279819</v>
@@ -9689,16 +9689,16 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>-0.07208448022448977</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.3287097758027088</v>
+      </c>
+      <c r="D23" t="n">
         <v>-0.06818193829026137</v>
       </c>
-      <c r="C23" t="n">
+      <c r="E23" t="n">
         <v>0.3386795885953031</v>
-      </c>
-      <c r="D23" t="n">
-        <v>-0.07208448022448977</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.3287097758027088</v>
       </c>
       <c r="F23" t="n">
         <v>-0.4068615268855644</v>
@@ -9714,16 +9714,16 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>-0.2173488963710079</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.09597449833476823</v>
+      </c>
+      <c r="D24" t="n">
         <v>-0.2155618399951673</v>
       </c>
-      <c r="C24" t="n">
+      <c r="E24" t="n">
         <v>-0.08361289843555031</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-0.2173488963710079</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-0.09597449833476823</v>
       </c>
       <c r="F24" t="n">
         <v>-0.131948941559617</v>
@@ -9739,16 +9739,16 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>-0.2334651826692295</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.2840335820907791</v>
+      </c>
+      <c r="D25" t="n">
         <v>-0.2254429466417733</v>
       </c>
-      <c r="C25" t="n">
+      <c r="E25" t="n">
         <v>-0.273575027597408</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-0.2334651826692295</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-0.2840335820907791</v>
       </c>
       <c r="F25" t="n">
         <v>0.04813208095563465</v>
@@ -9764,16 +9764,16 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>-0.1951209828401084</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.3245271077237757</v>
+      </c>
+      <c r="D26" t="n">
         <v>-0.1858585144416247</v>
       </c>
-      <c r="C26" t="n">
+      <c r="E26" t="n">
         <v>-0.3121996700922749</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-0.1951209828401084</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-0.3245271077237757</v>
       </c>
       <c r="F26" t="n">
         <v>0.1263411556506502</v>
@@ -9789,16 +9789,16 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>0.2790227155949912</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.2628132356581488</v>
+      </c>
+      <c r="D27" t="n">
         <v>0.282290181532039</v>
       </c>
-      <c r="C27" t="n">
+      <c r="E27" t="n">
         <v>-0.2575719702398097</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.2790227155949912</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-0.2628132356581488</v>
       </c>
       <c r="F27" t="n">
         <v>0.5398621517718487</v>
@@ -9814,16 +9814,16 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>0.2729350124049983</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.1413725677771169</v>
+      </c>
+      <c r="D28" t="n">
         <v>0.282052994639917</v>
       </c>
-      <c r="C28" t="n">
+      <c r="E28" t="n">
         <v>0.1512829934976888</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.2729350124049983</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.1413725677771169</v>
       </c>
       <c r="F28" t="n">
         <v>0.1307700011422282</v>
@@ -9839,16 +9839,16 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>0.1723785298030617</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.4021846571194039</v>
+      </c>
+      <c r="D29" t="n">
         <v>0.1777577531392439</v>
       </c>
-      <c r="C29" t="n">
+      <c r="E29" t="n">
         <v>-0.3901546342078486</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.1723785298030617</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-0.4021846571194039</v>
       </c>
       <c r="F29" t="n">
         <v>0.5679123873470925</v>
@@ -9864,16 +9864,16 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>0.09061815912915494</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.3127393308303081</v>
+      </c>
+      <c r="D30" t="n">
         <v>0.1012182419383847</v>
       </c>
-      <c r="C30" t="n">
+      <c r="E30" t="n">
         <v>-0.2928248716000603</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.09061815912915494</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-0.3127393308303081</v>
       </c>
       <c r="F30" t="n">
         <v>0.394043113538445</v>
@@ -9889,16 +9889,16 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>-0.2110528378632041</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.3907150346541115</v>
+      </c>
+      <c r="D31" t="n">
         <v>-0.1916952565215667</v>
       </c>
-      <c r="C31" t="n">
+      <c r="E31" t="n">
         <v>-0.3792681687753456</v>
-      </c>
-      <c r="D31" t="n">
-        <v>-0.2110528378632041</v>
-      </c>
-      <c r="E31" t="n">
-        <v>-0.3907150346541115</v>
       </c>
       <c r="F31" t="n">
         <v>0.187572912253779</v>
@@ -9914,16 +9914,16 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>-0.001998746514946581</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.2508264191124089</v>
+      </c>
+      <c r="D32" t="n">
         <v>0.008528727755699905</v>
       </c>
-      <c r="C32" t="n">
+      <c r="E32" t="n">
         <v>-0.235858693130374</v>
-      </c>
-      <c r="D32" t="n">
-        <v>-0.001998746514946581</v>
-      </c>
-      <c r="E32" t="n">
-        <v>-0.2508264191124089</v>
       </c>
       <c r="F32" t="n">
         <v>0.2443874208860739</v>
@@ -9939,16 +9939,16 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>-0.1707915628259661</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.2379377212213738</v>
+      </c>
+      <c r="D33" t="n">
         <v>-0.1586368358287528</v>
       </c>
-      <c r="C33" t="n">
+      <c r="E33" t="n">
         <v>-0.2270408621567945</v>
-      </c>
-      <c r="D33" t="n">
-        <v>-0.1707915628259661</v>
-      </c>
-      <c r="E33" t="n">
-        <v>-0.2379377212213738</v>
       </c>
       <c r="F33" t="n">
         <v>0.06840402632804177</v>
@@ -9964,16 +9964,16 @@
         </is>
       </c>
       <c r="B34" t="n">
+        <v>0.1182390458128568</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.003343267851642406</v>
+      </c>
+      <c r="D34" t="n">
         <v>0.1271008208560982</v>
       </c>
-      <c r="C34" t="n">
+      <c r="E34" t="n">
         <v>0.01248015692487348</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.1182390458128568</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.003343267851642406</v>
       </c>
       <c r="F34" t="n">
         <v>0.1146206639312247</v>
@@ -9989,16 +9989,16 @@
         </is>
       </c>
       <c r="B35" t="n">
+        <v>0.1744570532614445</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.1854377861474943</v>
+      </c>
+      <c r="D35" t="n">
         <v>0.1854433873613598</v>
       </c>
-      <c r="C35" t="n">
+      <c r="E35" t="n">
         <v>0.1905998686175449</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.1744570532614445</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.1854377861474943</v>
       </c>
       <c r="F35" t="n">
         <v>-0.005156481256185008</v>
@@ -10014,16 +10014,16 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>0.2056592770879171</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.2728407585803566</v>
+      </c>
+      <c r="D36" t="n">
         <v>0.2120321680177606</v>
       </c>
-      <c r="C36" t="n">
+      <c r="E36" t="n">
         <v>-0.263503400108836</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.2056592770879171</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.2728407585803566</v>
       </c>
       <c r="F36" t="n">
         <v>0.4755355681265966</v>
@@ -10039,16 +10039,16 @@
         </is>
       </c>
       <c r="B37" t="n">
+        <v>-0.05727973854662133</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.02091553062392526</v>
+      </c>
+      <c r="D37" t="n">
         <v>-0.04550521491040738</v>
       </c>
-      <c r="C37" t="n">
+      <c r="E37" t="n">
         <v>-0.01180110863191397</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-0.05727973854662133</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-0.02091553062392526</v>
       </c>
       <c r="F37" t="n">
         <v>-0.03370410627849341</v>
@@ -10064,16 +10064,16 @@
         </is>
       </c>
       <c r="B38" t="n">
+        <v>-0.1155950240621134</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.2580134776764273</v>
+      </c>
+      <c r="D38" t="n">
         <v>-0.1081878379166377</v>
       </c>
-      <c r="C38" t="n">
+      <c r="E38" t="n">
         <v>-0.252439080727934</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-0.1155950240621134</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-0.2580134776764273</v>
       </c>
       <c r="F38" t="n">
         <v>0.1442512428112964</v>
@@ -10089,16 +10089,16 @@
         </is>
       </c>
       <c r="B39" t="n">
+        <v>0.09053244021290524</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.2965308864239975</v>
+      </c>
+      <c r="D39" t="n">
         <v>0.09548493753193105</v>
       </c>
-      <c r="C39" t="n">
+      <c r="E39" t="n">
         <v>-0.2842593539696623</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.09053244021290524</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-0.2965308864239975</v>
       </c>
       <c r="F39" t="n">
         <v>0.3797442915015934</v>
@@ -10114,16 +10114,16 @@
         </is>
       </c>
       <c r="B40" t="n">
+        <v>-0.02339261005963666</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.351947960317155</v>
+      </c>
+      <c r="D40" t="n">
         <v>-0.01522654780539456</v>
       </c>
-      <c r="C40" t="n">
+      <c r="E40" t="n">
         <v>-0.3451595291067138</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-0.02339261005963666</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-0.351947960317155</v>
       </c>
       <c r="F40" t="n">
         <v>0.3299329813013192</v>
@@ -10139,16 +10139,16 @@
         </is>
       </c>
       <c r="B41" t="n">
+        <v>0.1956480185698567</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.2175857821986713</v>
+      </c>
+      <c r="D41" t="n">
         <v>0.2027758303693769</v>
       </c>
-      <c r="C41" t="n">
+      <c r="E41" t="n">
         <v>-0.2064253790402319</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.1956480185698567</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-0.2175857821986713</v>
       </c>
       <c r="F41" t="n">
         <v>0.4092012094096089</v>
@@ -10164,16 +10164,16 @@
         </is>
       </c>
       <c r="B42" t="n">
+        <v>0.2911771648094508</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.1823888883957793</v>
+      </c>
+      <c r="D42" t="n">
         <v>0.294537277274133</v>
       </c>
-      <c r="C42" t="n">
+      <c r="E42" t="n">
         <v>-0.1787230932344356</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.2911771648094508</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-0.1823888883957793</v>
       </c>
       <c r="F42" t="n">
         <v>0.4732603705085686</v>
@@ -10189,16 +10189,16 @@
         </is>
       </c>
       <c r="B43" t="n">
+        <v>0.1795843306478575</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.1296251067171743</v>
+      </c>
+      <c r="D43" t="n">
         <v>0.1904859131449045</v>
       </c>
-      <c r="C43" t="n">
+      <c r="E43" t="n">
         <v>-0.1166735285906</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.1795843306478575</v>
-      </c>
-      <c r="E43" t="n">
-        <v>-0.1296251067171743</v>
       </c>
       <c r="F43" t="n">
         <v>0.3071594417355045</v>
@@ -10214,16 +10214,16 @@
         </is>
       </c>
       <c r="B44" t="n">
+        <v>0.001730568762679074</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.2258474091519202</v>
+      </c>
+      <c r="D44" t="n">
         <v>0.009123982064009883</v>
       </c>
-      <c r="C44" t="n">
+      <c r="E44" t="n">
         <v>0.237884575098714</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.001730568762679074</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.2258474091519202</v>
       </c>
       <c r="F44" t="n">
         <v>-0.2287605930347041</v>
@@ -10239,16 +10239,16 @@
         </is>
       </c>
       <c r="B45" t="n">
+        <v>-0.01294450969930483</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.2493251628330669</v>
+      </c>
+      <c r="D45" t="n">
         <v>-0.001284185675907046</v>
       </c>
-      <c r="C45" t="n">
+      <c r="E45" t="n">
         <v>-0.23761454121298</v>
-      </c>
-      <c r="D45" t="n">
-        <v>-0.01294450969930483</v>
-      </c>
-      <c r="E45" t="n">
-        <v>-0.2493251628330669</v>
       </c>
       <c r="F45" t="n">
         <v>0.2363303555370729</v>
@@ -10264,16 +10264,16 @@
         </is>
       </c>
       <c r="B46" t="n">
+        <v>0.01863678404980562</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.1773867622707903</v>
+      </c>
+      <c r="D46" t="n">
         <v>0.02517382103302068</v>
       </c>
-      <c r="C46" t="n">
+      <c r="E46" t="n">
         <v>-0.1707181460121928</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.01863678404980562</v>
-      </c>
-      <c r="E46" t="n">
-        <v>-0.1773867622707903</v>
       </c>
       <c r="F46" t="n">
         <v>0.1958919670452135</v>
@@ -10289,16 +10289,16 @@
         </is>
       </c>
       <c r="B47" t="n">
+        <v>-0.1903658923856946</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.1509584985662013</v>
+      </c>
+      <c r="D47" t="n">
         <v>-0.1785080906540044</v>
       </c>
-      <c r="C47" t="n">
+      <c r="E47" t="n">
         <v>-0.1480870037865182</v>
-      </c>
-      <c r="D47" t="n">
-        <v>-0.1903658923856946</v>
-      </c>
-      <c r="E47" t="n">
-        <v>-0.1509584985662013</v>
       </c>
       <c r="F47" t="n">
         <v>-0.03042108686748624</v>
@@ -10314,16 +10314,16 @@
         </is>
       </c>
       <c r="B48" t="n">
+        <v>-0.07810699019270401</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.1623767883036991</v>
+      </c>
+      <c r="D48" t="n">
         <v>-0.06561323405303643</v>
       </c>
-      <c r="C48" t="n">
+      <c r="E48" t="n">
         <v>-0.1498781359978958</v>
-      </c>
-      <c r="D48" t="n">
-        <v>-0.07810699019270401</v>
-      </c>
-      <c r="E48" t="n">
-        <v>-0.1623767883036991</v>
       </c>
       <c r="F48" t="n">
         <v>0.08426490194485942</v>
@@ -10339,16 +10339,16 @@
         </is>
       </c>
       <c r="B49" t="n">
+        <v>-0.02393094622177633</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.1773974339882161</v>
+      </c>
+      <c r="D49" t="n">
         <v>-0.01643027180035156</v>
       </c>
-      <c r="C49" t="n">
+      <c r="E49" t="n">
         <v>-0.169674736526544</v>
-      </c>
-      <c r="D49" t="n">
-        <v>-0.02393094622177633</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-0.1773974339882161</v>
       </c>
       <c r="F49" t="n">
         <v>0.1532444647261924</v>
@@ -10364,16 +10364,16 @@
         </is>
       </c>
       <c r="B50" t="n">
+        <v>-0.1766630949081813</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.2568714354326989</v>
+      </c>
+      <c r="D50" t="n">
         <v>-0.1676058002285175</v>
       </c>
-      <c r="C50" t="n">
+      <c r="E50" t="n">
         <v>-0.2448343928541279</v>
-      </c>
-      <c r="D50" t="n">
-        <v>-0.1766630949081813</v>
-      </c>
-      <c r="E50" t="n">
-        <v>-0.2568714354326989</v>
       </c>
       <c r="F50" t="n">
         <v>0.07722859262561044</v>
@@ -10389,16 +10389,16 @@
         </is>
       </c>
       <c r="B51" t="n">
+        <v>0.2092226403793132</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.360530309978668</v>
+      </c>
+      <c r="D51" t="n">
         <v>0.2181889285389335</v>
       </c>
-      <c r="C51" t="n">
+      <c r="E51" t="n">
         <v>-0.3547268645191286</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.2092226403793132</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-0.360530309978668</v>
       </c>
       <c r="F51" t="n">
         <v>0.5729157930580621</v>
@@ -10414,16 +10414,16 @@
         </is>
       </c>
       <c r="B52" t="n">
+        <v>0.2490216291097824</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.1126740965160479</v>
+      </c>
+      <c r="D52" t="n">
         <v>0.2600100505867158</v>
       </c>
-      <c r="C52" t="n">
+      <c r="E52" t="n">
         <v>-0.09443705220358006</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.2490216291097824</v>
-      </c>
-      <c r="E52" t="n">
-        <v>-0.1126740965160479</v>
       </c>
       <c r="F52" t="n">
         <v>0.3544471027902958</v>
@@ -10439,16 +10439,16 @@
         </is>
       </c>
       <c r="B53" t="n">
+        <v>0.01662016230543933</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.200335092749018</v>
+      </c>
+      <c r="D53" t="n">
         <v>0.03390607113445931</v>
       </c>
-      <c r="C53" t="n">
+      <c r="E53" t="n">
         <v>-0.2002254589768854</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.01662016230543933</v>
-      </c>
-      <c r="E53" t="n">
-        <v>-0.200335092749018</v>
       </c>
       <c r="F53" t="n">
         <v>0.2341315301113447</v>
@@ -10464,16 +10464,16 @@
         </is>
       </c>
       <c r="B54" t="n">
+        <v>0.06974824115960998</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.3061780819936362</v>
+      </c>
+      <c r="D54" t="n">
         <v>0.07463771787505386</v>
       </c>
-      <c r="C54" t="n">
+      <c r="E54" t="n">
         <v>-0.3059115785148843</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.06974824115960998</v>
-      </c>
-      <c r="E54" t="n">
-        <v>-0.3061780819936362</v>
       </c>
       <c r="F54" t="n">
         <v>0.3805492963899382</v>
@@ -10489,16 +10489,16 @@
         </is>
       </c>
       <c r="B55" t="n">
+        <v>-0.3178689545974104</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.2915424317675782</v>
+      </c>
+      <c r="D55" t="n">
         <v>-0.3173394691324223</v>
       </c>
-      <c r="C55" t="n">
+      <c r="E55" t="n">
         <v>-0.2860545135770747</v>
-      </c>
-      <c r="D55" t="n">
-        <v>-0.3178689545974104</v>
-      </c>
-      <c r="E55" t="n">
-        <v>-0.2915424317675782</v>
       </c>
       <c r="F55" t="n">
         <v>-0.03128495555534766</v>
@@ -10514,16 +10514,16 @@
         </is>
       </c>
       <c r="B56" t="n">
+        <v>0.005063719645394871</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.2181679188367605</v>
+      </c>
+      <c r="D56" t="n">
         <v>0.00889190056471989</v>
       </c>
-      <c r="C56" t="n">
+      <c r="E56" t="n">
         <v>-0.1984815447500237</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0.005063719645394871</v>
-      </c>
-      <c r="E56" t="n">
-        <v>-0.2181679188367605</v>
       </c>
       <c r="F56" t="n">
         <v>0.2073734453147436</v>
@@ -10539,16 +10539,16 @@
         </is>
       </c>
       <c r="B57" t="n">
+        <v>0.2890748323673312</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.181151667746577</v>
+      </c>
+      <c r="D57" t="n">
         <v>0.2940113528206453</v>
       </c>
-      <c r="C57" t="n">
+      <c r="E57" t="n">
         <v>-0.1701784352732639</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0.2890748323673312</v>
-      </c>
-      <c r="E57" t="n">
-        <v>-0.181151667746577</v>
       </c>
       <c r="F57" t="n">
         <v>0.4641897880939092</v>
@@ -10564,16 +10564,16 @@
         </is>
       </c>
       <c r="B58" t="n">
+        <v>-0.2376292974927998</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.2331315445940539</v>
+      </c>
+      <c r="D58" t="n">
         <v>-0.2328361142960023</v>
       </c>
-      <c r="C58" t="n">
+      <c r="E58" t="n">
         <v>-0.2222798729160096</v>
-      </c>
-      <c r="D58" t="n">
-        <v>-0.2376292974927998</v>
-      </c>
-      <c r="E58" t="n">
-        <v>-0.2331315445940539</v>
       </c>
       <c r="F58" t="n">
         <v>-0.01055624137999267</v>
@@ -10589,16 +10589,16 @@
         </is>
       </c>
       <c r="B59" t="n">
+        <v>-0.2429247746241763</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.4007624257910878</v>
+      </c>
+      <c r="D59" t="n">
         <v>-0.2299466189094422</v>
       </c>
-      <c r="C59" t="n">
+      <c r="E59" t="n">
         <v>-0.3925134343582949</v>
-      </c>
-      <c r="D59" t="n">
-        <v>-0.2429247746241763</v>
-      </c>
-      <c r="E59" t="n">
-        <v>-0.4007624257910878</v>
       </c>
       <c r="F59" t="n">
         <v>0.1625668154488527</v>
@@ -10614,16 +10614,16 @@
         </is>
       </c>
       <c r="B60" t="n">
+        <v>-0.1827073058158354</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.04318429419060787</v>
+      </c>
+      <c r="D60" t="n">
         <v>-0.171768430530216</v>
       </c>
-      <c r="C60" t="n">
+      <c r="E60" t="n">
         <v>0.0535955550021493</v>
-      </c>
-      <c r="D60" t="n">
-        <v>-0.1827073058158354</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0.04318429419060787</v>
       </c>
       <c r="F60" t="n">
         <v>-0.2253639855323653</v>
@@ -10639,16 +10639,16 @@
         </is>
       </c>
       <c r="B61" t="n">
+        <v>0.00659670753889241</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.10496146511462</v>
+      </c>
+      <c r="D61" t="n">
         <v>0.01702883081564338</v>
       </c>
-      <c r="C61" t="n">
+      <c r="E61" t="n">
         <v>0.118762934754211</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0.00659670753889241</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0.10496146511462</v>
       </c>
       <c r="F61" t="n">
         <v>-0.1017341039385676</v>
@@ -10664,16 +10664,16 @@
         </is>
       </c>
       <c r="B62" t="n">
+        <v>0.3934694267007109</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.1506741303762525</v>
+      </c>
+      <c r="D62" t="n">
         <v>0.403528959292164</v>
       </c>
-      <c r="C62" t="n">
+      <c r="E62" t="n">
         <v>-0.138173420977198</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0.3934694267007109</v>
-      </c>
-      <c r="E62" t="n">
-        <v>-0.1506741303762525</v>
       </c>
       <c r="F62" t="n">
         <v>0.541702380269362</v>
@@ -10689,16 +10689,16 @@
         </is>
       </c>
       <c r="B63" t="n">
+        <v>-0.1300422529330991</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.1226850797144828</v>
+      </c>
+      <c r="D63" t="n">
         <v>-0.1189164035526579</v>
       </c>
-      <c r="C63" t="n">
+      <c r="E63" t="n">
         <v>-0.1167391742835678</v>
-      </c>
-      <c r="D63" t="n">
-        <v>-0.1300422529330991</v>
-      </c>
-      <c r="E63" t="n">
-        <v>-0.1226850797144828</v>
       </c>
       <c r="F63" t="n">
         <v>-0.002177229269090031</v>
@@ -10714,16 +10714,16 @@
         </is>
       </c>
       <c r="B64" t="n">
+        <v>0.31408368368783</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.2537348874181068</v>
+      </c>
+      <c r="D64" t="n">
         <v>0.321766558782817</v>
       </c>
-      <c r="C64" t="n">
+      <c r="E64" t="n">
         <v>-0.2362411491461038</v>
-      </c>
-      <c r="D64" t="n">
-        <v>0.31408368368783</v>
-      </c>
-      <c r="E64" t="n">
-        <v>-0.2537348874181068</v>
       </c>
       <c r="F64" t="n">
         <v>0.5580077079289207</v>
@@ -10739,16 +10739,16 @@
         </is>
       </c>
       <c r="B65" t="n">
+        <v>-0.2471454285929376</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.3382333405327361</v>
+      </c>
+      <c r="D65" t="n">
         <v>-0.2381180692050073</v>
       </c>
-      <c r="C65" t="n">
+      <c r="E65" t="n">
         <v>-0.3271473806588898</v>
-      </c>
-      <c r="D65" t="n">
-        <v>-0.2471454285929376</v>
-      </c>
-      <c r="E65" t="n">
-        <v>-0.3382333405327361</v>
       </c>
       <c r="F65" t="n">
         <v>0.08902931145388249</v>
@@ -10764,16 +10764,16 @@
         </is>
       </c>
       <c r="B66" t="n">
+        <v>-0.1636481074939865</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.1394940989552976</v>
+      </c>
+      <c r="D66" t="n">
         <v>-0.1593925529787303</v>
       </c>
-      <c r="C66" t="n">
+      <c r="E66" t="n">
         <v>-0.1311696188669709</v>
-      </c>
-      <c r="D66" t="n">
-        <v>-0.1636481074939865</v>
-      </c>
-      <c r="E66" t="n">
-        <v>-0.1394940989552976</v>
       </c>
       <c r="F66" t="n">
         <v>-0.02822293411175941</v>
@@ -10789,16 +10789,16 @@
         </is>
       </c>
       <c r="B67" t="n">
+        <v>0.02270187832088888</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.3227956513634979</v>
+      </c>
+      <c r="D67" t="n">
         <v>0.02421054206770556</v>
       </c>
-      <c r="C67" t="n">
+      <c r="E67" t="n">
         <v>-0.3119282977657173</v>
-      </c>
-      <c r="D67" t="n">
-        <v>0.02270187832088888</v>
-      </c>
-      <c r="E67" t="n">
-        <v>-0.3227956513634979</v>
       </c>
       <c r="F67" t="n">
         <v>0.3361388398334229</v>
@@ -10814,16 +10814,16 @@
         </is>
       </c>
       <c r="B68" t="n">
+        <v>-0.3791405606132182</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.3417960833276626</v>
+      </c>
+      <c r="D68" t="n">
         <v>-0.3683494893489501</v>
       </c>
-      <c r="C68" t="n">
+      <c r="E68" t="n">
         <v>-0.3318708521615392</v>
-      </c>
-      <c r="D68" t="n">
-        <v>-0.3791405606132182</v>
-      </c>
-      <c r="E68" t="n">
-        <v>-0.3417960833276626</v>
       </c>
       <c r="F68" t="n">
         <v>-0.0364786371874109</v>
@@ -10839,16 +10839,16 @@
         </is>
       </c>
       <c r="B69" t="n">
+        <v>0.07398469518747874</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.04582003169709659</v>
+      </c>
+      <c r="D69" t="n">
         <v>0.07740936665173415</v>
       </c>
-      <c r="C69" t="n">
+      <c r="E69" t="n">
         <v>-0.03660351406120399</v>
-      </c>
-      <c r="D69" t="n">
-        <v>0.07398469518747874</v>
-      </c>
-      <c r="E69" t="n">
-        <v>-0.04582003169709659</v>
       </c>
       <c r="F69" t="n">
         <v>0.1140128807129381</v>
@@ -10864,16 +10864,16 @@
         </is>
       </c>
       <c r="B70" t="n">
+        <v>-0.2488607356080158</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.4015563941709165</v>
+      </c>
+      <c r="D70" t="n">
         <v>-0.2299061879927619</v>
       </c>
-      <c r="C70" t="n">
+      <c r="E70" t="n">
         <v>-0.385577739223323</v>
-      </c>
-      <c r="D70" t="n">
-        <v>-0.2488607356080158</v>
-      </c>
-      <c r="E70" t="n">
-        <v>-0.4015563941709165</v>
       </c>
       <c r="F70" t="n">
         <v>0.1556715512305611</v>
@@ -10889,16 +10889,16 @@
         </is>
       </c>
       <c r="B71" t="n">
+        <v>0.03007627750771802</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.2505759686566277</v>
+      </c>
+      <c r="D71" t="n">
         <v>0.04409624032524612</v>
       </c>
-      <c r="C71" t="n">
+      <c r="E71" t="n">
         <v>-0.2348577567185384</v>
-      </c>
-      <c r="D71" t="n">
-        <v>0.03007627750771802</v>
-      </c>
-      <c r="E71" t="n">
-        <v>-0.2505759686566277</v>
       </c>
       <c r="F71" t="n">
         <v>0.2789539970437845</v>
@@ -10914,16 +10914,16 @@
         </is>
       </c>
       <c r="B72" t="n">
+        <v>-0.1724109723171459</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.2375373201916289</v>
+      </c>
+      <c r="D72" t="n">
         <v>-0.1693948040430185</v>
       </c>
-      <c r="C72" t="n">
+      <c r="E72" t="n">
         <v>-0.2262223090047014</v>
-      </c>
-      <c r="D72" t="n">
-        <v>-0.1724109723171459</v>
-      </c>
-      <c r="E72" t="n">
-        <v>-0.2375373201916289</v>
       </c>
       <c r="F72" t="n">
         <v>0.05682750496168287</v>
@@ -10939,16 +10939,16 @@
         </is>
       </c>
       <c r="B73" t="n">
+        <v>-0.3704673349290366</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.1070708325895594</v>
+      </c>
+      <c r="D73" t="n">
         <v>-0.3584373639913001</v>
       </c>
-      <c r="C73" t="n">
+      <c r="E73" t="n">
         <v>-0.09053534887067199</v>
-      </c>
-      <c r="D73" t="n">
-        <v>-0.3704673349290366</v>
-      </c>
-      <c r="E73" t="n">
-        <v>-0.1070708325895594</v>
       </c>
       <c r="F73" t="n">
         <v>-0.2679020151206281</v>
@@ -10964,16 +10964,16 @@
         </is>
       </c>
       <c r="B74" t="n">
+        <v>-0.1605771718444837</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.2160799441076506</v>
+      </c>
+      <c r="D74" t="n">
         <v>-0.159754149325234</v>
       </c>
-      <c r="C74" t="n">
+      <c r="E74" t="n">
         <v>-0.203923831416286</v>
-      </c>
-      <c r="D74" t="n">
-        <v>-0.1605771718444837</v>
-      </c>
-      <c r="E74" t="n">
-        <v>-0.2160799441076506</v>
       </c>
       <c r="F74" t="n">
         <v>0.04416968209105193</v>
@@ -10989,16 +10989,16 @@
         </is>
       </c>
       <c r="B75" t="n">
+        <v>0.06014538437742745</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.1705775778382003</v>
+      </c>
+      <c r="D75" t="n">
         <v>0.06591725674659032</v>
       </c>
-      <c r="C75" t="n">
+      <c r="E75" t="n">
         <v>-0.1671454317786639</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0.06014538437742745</v>
-      </c>
-      <c r="E75" t="n">
-        <v>-0.1705775778382003</v>
       </c>
       <c r="F75" t="n">
         <v>0.2330626885252542</v>
@@ -11014,16 +11014,16 @@
         </is>
       </c>
       <c r="B76" t="n">
+        <v>0.286889846508076</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.3446216598798324</v>
+      </c>
+      <c r="D76" t="n">
         <v>0.2925491890111084</v>
       </c>
-      <c r="C76" t="n">
+      <c r="E76" t="n">
         <v>-0.3291747442260283</v>
-      </c>
-      <c r="D76" t="n">
-        <v>0.286889846508076</v>
-      </c>
-      <c r="E76" t="n">
-        <v>-0.3446216598798324</v>
       </c>
       <c r="F76" t="n">
         <v>0.6217239332371367</v>
@@ -11039,16 +11039,16 @@
         </is>
       </c>
       <c r="B77" t="n">
+        <v>0.1853822537680984</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-0.2444068448239417</v>
+      </c>
+      <c r="D77" t="n">
         <v>0.1863883679778391</v>
       </c>
-      <c r="C77" t="n">
+      <c r="E77" t="n">
         <v>-0.2353337552595551</v>
-      </c>
-      <c r="D77" t="n">
-        <v>0.1853822537680984</v>
-      </c>
-      <c r="E77" t="n">
-        <v>-0.2444068448239417</v>
       </c>
       <c r="F77" t="n">
         <v>0.4217221232373942</v>
@@ -11064,16 +11064,16 @@
         </is>
       </c>
       <c r="B78" t="n">
+        <v>0.326730650947642</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.2766768362339694</v>
+      </c>
+      <c r="D78" t="n">
         <v>0.3354024800563348</v>
       </c>
-      <c r="C78" t="n">
+      <c r="E78" t="n">
         <v>-0.2674284726875145</v>
-      </c>
-      <c r="D78" t="n">
-        <v>0.326730650947642</v>
-      </c>
-      <c r="E78" t="n">
-        <v>-0.2766768362339694</v>
       </c>
       <c r="F78" t="n">
         <v>0.6028309527438493</v>
@@ -11089,16 +11089,16 @@
         </is>
       </c>
       <c r="B79" t="n">
+        <v>0.1975624679684108</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.1428790428015999</v>
+      </c>
+      <c r="D79" t="n">
         <v>0.2032358262635371</v>
       </c>
-      <c r="C79" t="n">
+      <c r="E79" t="n">
         <v>-0.1421079540557695</v>
-      </c>
-      <c r="D79" t="n">
-        <v>0.1975624679684108</v>
-      </c>
-      <c r="E79" t="n">
-        <v>-0.1428790428015999</v>
       </c>
       <c r="F79" t="n">
         <v>0.3453437803193066</v>
@@ -11114,16 +11114,16 @@
         </is>
       </c>
       <c r="B80" t="n">
+        <v>-0.04539305615961498</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.2017254527487418</v>
+      </c>
+      <c r="D80" t="n">
         <v>-0.0385498898849555</v>
       </c>
-      <c r="C80" t="n">
+      <c r="E80" t="n">
         <v>-0.1917551586475985</v>
-      </c>
-      <c r="D80" t="n">
-        <v>-0.04539305615961498</v>
-      </c>
-      <c r="E80" t="n">
-        <v>-0.2017254527487418</v>
       </c>
       <c r="F80" t="n">
         <v>0.153205268762643</v>
@@ -11139,16 +11139,16 @@
         </is>
       </c>
       <c r="B81" t="n">
+        <v>-0.1211136621323579</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.4083242436764424</v>
+      </c>
+      <c r="D81" t="n">
         <v>-0.1003392450746688</v>
       </c>
-      <c r="C81" t="n">
+      <c r="E81" t="n">
         <v>-0.3931195083048597</v>
-      </c>
-      <c r="D81" t="n">
-        <v>-0.1211136621323579</v>
-      </c>
-      <c r="E81" t="n">
-        <v>-0.4083242436764424</v>
       </c>
       <c r="F81" t="n">
         <v>0.2927802632301909</v>
@@ -11164,16 +11164,16 @@
         </is>
       </c>
       <c r="B82" t="n">
+        <v>-0.1836894407773513</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.08627004039226571</v>
+      </c>
+      <c r="D82" t="n">
         <v>-0.1717473000681943</v>
       </c>
-      <c r="C82" t="n">
+      <c r="E82" t="n">
         <v>-0.0773780374776124</v>
-      </c>
-      <c r="D82" t="n">
-        <v>-0.1836894407773513</v>
-      </c>
-      <c r="E82" t="n">
-        <v>-0.08627004039226571</v>
       </c>
       <c r="F82" t="n">
         <v>-0.09436926259058187</v>
@@ -11189,16 +11189,16 @@
         </is>
       </c>
       <c r="B83" t="n">
+        <v>0.2390310606561188</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.2806183037746897</v>
+      </c>
+      <c r="D83" t="n">
         <v>0.2540674285237416</v>
       </c>
-      <c r="C83" t="n">
+      <c r="E83" t="n">
         <v>-0.2750077146625198</v>
-      </c>
-      <c r="D83" t="n">
-        <v>0.2390310606561188</v>
-      </c>
-      <c r="E83" t="n">
-        <v>-0.2806183037746897</v>
       </c>
       <c r="F83" t="n">
         <v>0.5290751431862615</v>
@@ -11214,16 +11214,16 @@
         </is>
       </c>
       <c r="B84" t="n">
+        <v>0.2979952375457731</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.2798140458375124</v>
+      </c>
+      <c r="D84" t="n">
         <v>0.3031334859045485</v>
       </c>
-      <c r="C84" t="n">
+      <c r="E84" t="n">
         <v>-0.2563746745553541</v>
-      </c>
-      <c r="D84" t="n">
-        <v>0.2979952375457731</v>
-      </c>
-      <c r="E84" t="n">
-        <v>-0.2798140458375124</v>
       </c>
       <c r="F84" t="n">
         <v>0.5595081604599026</v>
@@ -11239,16 +11239,16 @@
         </is>
       </c>
       <c r="B85" t="n">
+        <v>-0.1263377903882385</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.2965841628261632</v>
+      </c>
+      <c r="D85" t="n">
         <v>-0.1181004962359042</v>
       </c>
-      <c r="C85" t="n">
+      <c r="E85" t="n">
         <v>-0.2823241496423203</v>
-      </c>
-      <c r="D85" t="n">
-        <v>-0.1263377903882385</v>
-      </c>
-      <c r="E85" t="n">
-        <v>-0.2965841628261632</v>
       </c>
       <c r="F85" t="n">
         <v>0.164223653406416</v>
@@ -11264,16 +11264,16 @@
         </is>
       </c>
       <c r="B86" t="n">
+        <v>0.04386317485771307</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.3158779047042343</v>
+      </c>
+      <c r="D86" t="n">
         <v>0.04642574483472917</v>
       </c>
-      <c r="C86" t="n">
+      <c r="E86" t="n">
         <v>-0.3046475177455866</v>
-      </c>
-      <c r="D86" t="n">
-        <v>0.04386317485771307</v>
-      </c>
-      <c r="E86" t="n">
-        <v>-0.3158779047042343</v>
       </c>
       <c r="F86" t="n">
         <v>0.3510732625803157</v>
@@ -11289,16 +11289,16 @@
         </is>
       </c>
       <c r="B87" t="n">
+        <v>-0.3656375136879055</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.2631320064735452</v>
+      </c>
+      <c r="D87" t="n">
         <v>-0.3512117291129341</v>
       </c>
-      <c r="C87" t="n">
+      <c r="E87" t="n">
         <v>-0.2423945307941151</v>
-      </c>
-      <c r="D87" t="n">
-        <v>-0.3656375136879055</v>
-      </c>
-      <c r="E87" t="n">
-        <v>-0.2631320064735452</v>
       </c>
       <c r="F87" t="n">
         <v>-0.108817198318819</v>
@@ -11314,16 +11314,16 @@
         </is>
       </c>
       <c r="B88" t="n">
+        <v>-0.01337635058658693</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-0.2473671225302185</v>
+      </c>
+      <c r="D88" t="n">
         <v>-0.01082190118592197</v>
       </c>
-      <c r="C88" t="n">
+      <c r="E88" t="n">
         <v>-0.2378240899920145</v>
-      </c>
-      <c r="D88" t="n">
-        <v>-0.01337635058658693</v>
-      </c>
-      <c r="E88" t="n">
-        <v>-0.2473671225302185</v>
       </c>
       <c r="F88" t="n">
         <v>0.2270021888060925</v>
@@ -11339,16 +11339,16 @@
         </is>
       </c>
       <c r="B89" t="n">
+        <v>-0.3226219822092567</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.2985656628266566</v>
+      </c>
+      <c r="D89" t="n">
         <v>-0.3074856901358264</v>
       </c>
-      <c r="C89" t="n">
+      <c r="E89" t="n">
         <v>-0.2882916622201455</v>
-      </c>
-      <c r="D89" t="n">
-        <v>-0.3226219822092567</v>
-      </c>
-      <c r="E89" t="n">
-        <v>-0.2985656628266566</v>
       </c>
       <c r="F89" t="n">
         <v>-0.01919402791568092</v>
@@ -11364,16 +11364,16 @@
         </is>
       </c>
       <c r="B90" t="n">
+        <v>0.3249078049086778</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.3573839983904897</v>
+      </c>
+      <c r="D90" t="n">
         <v>0.3262328668190944</v>
       </c>
-      <c r="C90" t="n">
+      <c r="E90" t="n">
         <v>-0.3467720588087164</v>
-      </c>
-      <c r="D90" t="n">
-        <v>0.3249078049086778</v>
-      </c>
-      <c r="E90" t="n">
-        <v>-0.3573839983904897</v>
       </c>
       <c r="F90" t="n">
         <v>0.6730049256278108</v>
@@ -11389,16 +11389,16 @@
         </is>
       </c>
       <c r="B91" t="n">
+        <v>-0.2060079673390383</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.3407053080637584</v>
+      </c>
+      <c r="D91" t="n">
         <v>-0.1906256163554488</v>
       </c>
-      <c r="C91" t="n">
+      <c r="E91" t="n">
         <v>-0.3311193366118786</v>
-      </c>
-      <c r="D91" t="n">
-        <v>-0.2060079673390383</v>
-      </c>
-      <c r="E91" t="n">
-        <v>-0.3407053080637584</v>
       </c>
       <c r="F91" t="n">
         <v>0.1404937202564299</v>
@@ -11414,16 +11414,16 @@
         </is>
       </c>
       <c r="B92" t="n">
+        <v>0.4383247219929261</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.2646006928521109</v>
+      </c>
+      <c r="D92" t="n">
         <v>0.448837223325309</v>
       </c>
-      <c r="C92" t="n">
+      <c r="E92" t="n">
         <v>-0.2575969176728913</v>
-      </c>
-      <c r="D92" t="n">
-        <v>0.4383247219929261</v>
-      </c>
-      <c r="E92" t="n">
-        <v>-0.2646006928521109</v>
       </c>
       <c r="F92" t="n">
         <v>0.7064341409982003</v>
@@ -11439,16 +11439,16 @@
         </is>
       </c>
       <c r="B93" t="n">
+        <v>-0.1815747600445639</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.2697523298615116</v>
+      </c>
+      <c r="D93" t="n">
         <v>-0.1637515063323567</v>
       </c>
-      <c r="C93" t="n">
+      <c r="E93" t="n">
         <v>-0.2490507470666137</v>
-      </c>
-      <c r="D93" t="n">
-        <v>-0.1815747600445639</v>
-      </c>
-      <c r="E93" t="n">
-        <v>-0.2697523298615116</v>
       </c>
       <c r="F93" t="n">
         <v>0.08529924073425693</v>
@@ -11464,16 +11464,16 @@
         </is>
       </c>
       <c r="B94" t="n">
+        <v>0.3656168852622309</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-0.2583211987235688</v>
+      </c>
+      <c r="D94" t="n">
         <v>0.3708897517186754</v>
       </c>
-      <c r="C94" t="n">
+      <c r="E94" t="n">
         <v>-0.2485243155234326</v>
-      </c>
-      <c r="D94" t="n">
-        <v>0.3656168852622309</v>
-      </c>
-      <c r="E94" t="n">
-        <v>-0.2583211987235688</v>
       </c>
       <c r="F94" t="n">
         <v>0.619414067242108</v>
@@ -11489,16 +11489,16 @@
         </is>
       </c>
       <c r="B95" t="n">
+        <v>-0.05084275748302303</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.06180104565571926</v>
+      </c>
+      <c r="D95" t="n">
         <v>-0.02238924491874739</v>
       </c>
-      <c r="C95" t="n">
+      <c r="E95" t="n">
         <v>0.07445856343131868</v>
-      </c>
-      <c r="D95" t="n">
-        <v>-0.05084275748302303</v>
-      </c>
-      <c r="E95" t="n">
-        <v>0.06180104565571926</v>
       </c>
       <c r="F95" t="n">
         <v>-0.09684780835006607</v>
@@ -11514,16 +11514,16 @@
         </is>
       </c>
       <c r="B96" t="n">
+        <v>0.3566295075575648</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.2750963289949535</v>
+      </c>
+      <c r="D96" t="n">
         <v>0.3680618401331509</v>
       </c>
-      <c r="C96" t="n">
+      <c r="E96" t="n">
         <v>0.2898251480225861</v>
-      </c>
-      <c r="D96" t="n">
-        <v>0.3566295075575648</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0.2750963289949535</v>
       </c>
       <c r="F96" t="n">
         <v>0.07823669211056478</v>
@@ -11539,16 +11539,16 @@
         </is>
       </c>
       <c r="B97" t="n">
+        <v>0.1761310952066771</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-0.1952169584397216</v>
+      </c>
+      <c r="D97" t="n">
         <v>0.2012011685388694</v>
       </c>
-      <c r="C97" t="n">
+      <c r="E97" t="n">
         <v>-0.1761033402432755</v>
-      </c>
-      <c r="D97" t="n">
-        <v>0.1761310952066771</v>
-      </c>
-      <c r="E97" t="n">
-        <v>-0.1952169584397216</v>
       </c>
       <c r="F97" t="n">
         <v>0.3773045087821449</v>
@@ -11564,16 +11564,16 @@
         </is>
       </c>
       <c r="B98" t="n">
+        <v>-0.2949278029756874</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.007855320933923715</v>
+      </c>
+      <c r="D98" t="n">
         <v>-0.2781761542251417</v>
       </c>
-      <c r="C98" t="n">
+      <c r="E98" t="n">
         <v>0.02865707705552845</v>
-      </c>
-      <c r="D98" t="n">
-        <v>-0.2949278029756874</v>
-      </c>
-      <c r="E98" t="n">
-        <v>0.007855320933923715</v>
       </c>
       <c r="F98" t="n">
         <v>-0.3068332312806702</v>
@@ -11589,16 +11589,16 @@
         </is>
       </c>
       <c r="B99" t="n">
+        <v>0.219831387686523</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.2206198784385777</v>
+      </c>
+      <c r="D99" t="n">
         <v>0.2309263938129483</v>
       </c>
-      <c r="C99" t="n">
+      <c r="E99" t="n">
         <v>-0.2147694468069535</v>
-      </c>
-      <c r="D99" t="n">
-        <v>0.219831387686523</v>
-      </c>
-      <c r="E99" t="n">
-        <v>-0.2206198784385777</v>
       </c>
       <c r="F99" t="n">
         <v>0.4456958406199019</v>
@@ -11614,16 +11614,16 @@
         </is>
       </c>
       <c r="B100" t="n">
+        <v>-0.09589995657346562</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.4075906853535548</v>
+      </c>
+      <c r="D100" t="n">
         <v>-0.09137716260645801</v>
       </c>
-      <c r="C100" t="n">
+      <c r="E100" t="n">
         <v>-0.3996994317256232</v>
-      </c>
-      <c r="D100" t="n">
-        <v>-0.09589995657346562</v>
-      </c>
-      <c r="E100" t="n">
-        <v>-0.4075906853535548</v>
       </c>
       <c r="F100" t="n">
         <v>0.3083222691191652</v>
@@ -11639,16 +11639,16 @@
         </is>
       </c>
       <c r="B101" t="n">
+        <v>-0.2309688267504822</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.2550138087174576</v>
+      </c>
+      <c r="D101" t="n">
         <v>-0.2220791050676874</v>
       </c>
-      <c r="C101" t="n">
+      <c r="E101" t="n">
         <v>-0.2396409509685524</v>
-      </c>
-      <c r="D101" t="n">
-        <v>-0.2309688267504822</v>
-      </c>
-      <c r="E101" t="n">
-        <v>-0.2550138087174576</v>
       </c>
       <c r="F101" t="n">
         <v>0.01756184590086496</v>
@@ -11664,16 +11664,16 @@
         </is>
       </c>
       <c r="B102" t="n">
+        <v>-0.1275868785460758</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-0.1687073357311619</v>
+      </c>
+      <c r="D102" t="n">
         <v>-0.1169196223234599</v>
       </c>
-      <c r="C102" t="n">
+      <c r="E102" t="n">
         <v>-0.158265280516637</v>
-      </c>
-      <c r="D102" t="n">
-        <v>-0.1275868785460758</v>
-      </c>
-      <c r="E102" t="n">
-        <v>-0.1687073357311619</v>
       </c>
       <c r="F102" t="n">
         <v>0.04134565819317715</v>
@@ -11689,16 +11689,16 @@
         </is>
       </c>
       <c r="B103" t="n">
+        <v>-0.3264810634339704</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.3873437211838974</v>
+      </c>
+      <c r="D103" t="n">
         <v>-0.3175488316336101</v>
       </c>
-      <c r="C103" t="n">
+      <c r="E103" t="n">
         <v>-0.3820271316857154</v>
-      </c>
-      <c r="D103" t="n">
-        <v>-0.3264810634339704</v>
-      </c>
-      <c r="E103" t="n">
-        <v>-0.3873437211838974</v>
       </c>
       <c r="F103" t="n">
         <v>0.06447830005210536</v>
@@ -11714,16 +11714,16 @@
         </is>
       </c>
       <c r="B104" t="n">
+        <v>-0.2099029839387572</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.3435184746865383</v>
+      </c>
+      <c r="D104" t="n">
         <v>-0.2152213810098649</v>
       </c>
-      <c r="C104" t="n">
+      <c r="E104" t="n">
         <v>-0.3395029866962018</v>
-      </c>
-      <c r="D104" t="n">
-        <v>-0.2099029839387572</v>
-      </c>
-      <c r="E104" t="n">
-        <v>-0.3435184746865383</v>
       </c>
       <c r="F104" t="n">
         <v>0.1242816056863368</v>
@@ -11739,16 +11739,16 @@
         </is>
       </c>
       <c r="B105" t="n">
+        <v>0.09518000808042559</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.1757967421223247</v>
+      </c>
+      <c r="D105" t="n">
         <v>0.09365839355696115</v>
       </c>
-      <c r="C105" t="n">
+      <c r="E105" t="n">
         <v>-0.1794940351487807</v>
-      </c>
-      <c r="D105" t="n">
-        <v>0.09518000808042559</v>
-      </c>
-      <c r="E105" t="n">
-        <v>-0.1757967421223247</v>
       </c>
       <c r="F105" t="n">
         <v>0.2731524287057419</v>
@@ -11764,16 +11764,16 @@
         </is>
       </c>
       <c r="B106" t="n">
+        <v>0.02896015640127159</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.2786221049935911</v>
+      </c>
+      <c r="D106" t="n">
         <v>0.03253733428895256</v>
       </c>
-      <c r="C106" t="n">
+      <c r="E106" t="n">
         <v>-0.2652092860582789</v>
-      </c>
-      <c r="D106" t="n">
-        <v>0.02896015640127159</v>
-      </c>
-      <c r="E106" t="n">
-        <v>-0.2786221049935911</v>
       </c>
       <c r="F106" t="n">
         <v>0.2977466203472315</v>
